--- a/Задание/ПУ/Модуль 1/import/user_import.xlsx
+++ b/Задание/ПУ/Модуль 1/import/user_import.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\st53\Desktop\Прил_ОЗ_КОД 09.02.07-2-2026\ПУ\Модуль 1\Прил_2_ОЗ_КОД 09.02.07-2-2026-М1\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Новая папка (2)\Пример\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2130" windowWidth="26760" windowHeight="16560"/>
+    <workbookView xWindow="7200" yWindow="2136" windowWidth="26760" windowHeight="16560"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+  <si>
+    <t>Роль сотрудника</t>
+  </si>
+  <si>
+    <t>ФИО</t>
+  </si>
+  <si>
+    <t>Логин</t>
+  </si>
+  <si>
+    <t>Пароль</t>
+  </si>
   <si>
     <t>Администратор</t>
   </si>
@@ -129,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -145,6 +157,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
@@ -154,12 +173,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -173,14 +198,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,178 +526,192 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
     <col min="2" max="2" width="38.5" customWidth="1"/>
     <col min="3" max="3" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1"/>
-    <hyperlink ref="C2" r:id="rId2"/>
-    <hyperlink ref="C3" r:id="rId3"/>
-    <hyperlink ref="C4" r:id="rId4"/>
-    <hyperlink ref="C5" r:id="rId5"/>
-    <hyperlink ref="C6" r:id="rId6"/>
-    <hyperlink ref="C7" r:id="rId7"/>
-    <hyperlink ref="C8" r:id="rId8"/>
-    <hyperlink ref="C9" r:id="rId9"/>
-    <hyperlink ref="C10" r:id="rId10"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
